--- a/MRP_AI_Predictions.xlsx
+++ b/MRP_AI_Predictions.xlsx
@@ -516,7 +516,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>153.4328460693359</v>
+        <v>152.2281341552734</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -528,7 +528,7 @@
         <v>60</v>
       </c>
       <c r="F2">
-        <v>76.43284606933594</v>
+        <v>75.22813415527344</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -536,7 +536,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>158.7920532226562</v>
+        <v>157.7231140136719</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -548,7 +548,7 @@
         <v>80</v>
       </c>
       <c r="F3">
-        <v>80.79205322265625</v>
+        <v>79.72311401367188</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -556,7 +556,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>302.7594299316406</v>
+        <v>315.9134216308594</v>
       </c>
       <c r="C4">
         <v>250</v>
@@ -568,7 +568,7 @@
         <v>500</v>
       </c>
       <c r="F4">
-        <v>-22.24057006835938</v>
+        <v>-9.086578369140625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -576,7 +576,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>152.9817657470703</v>
+        <v>151.5955505371094</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>135.9817657470703</v>
+        <v>134.5955505371094</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -596,7 +596,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>153.0236511230469</v>
+        <v>151.7098388671875</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>136.0236511230469</v>
+        <v>134.7098388671875</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -616,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>153.1784210205078</v>
+        <v>151.8041076660156</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>136.1784210205078</v>
+        <v>134.8041076660156</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -636,7 +636,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>152.4496459960938</v>
+        <v>151.3575897216797</v>
       </c>
       <c r="C8">
         <v>25</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>135.4496459960938</v>
+        <v>134.3575897216797</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -656,7 +656,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>153.0320739746094</v>
+        <v>151.80029296875</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>136.0320739746094</v>
+        <v>134.80029296875</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -676,7 +676,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>152.7441558837891</v>
+        <v>151.5839385986328</v>
       </c>
       <c r="C10">
         <v>25</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>135.7441558837891</v>
+        <v>134.5839385986328</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -696,7 +696,7 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>153.5006256103516</v>
+        <v>151.9650268554688</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>136.5006256103516</v>
+        <v>134.9650268554688</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -716,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>152.7609405517578</v>
+        <v>151.5505676269531</v>
       </c>
       <c r="C12">
         <v>25</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>135.7609405517578</v>
+        <v>134.5505676269531</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -736,7 +736,7 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>153.5470886230469</v>
+        <v>151.8899536132812</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>136.5470886230469</v>
+        <v>134.8899536132812</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -756,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>152.7333984375</v>
+        <v>151.6146850585938</v>
       </c>
       <c r="C14">
         <v>25</v>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>135.7333984375</v>
+        <v>134.6146850585938</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -776,7 +776,7 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>158.0364685058594</v>
+        <v>156.8740539550781</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -788,7 +788,7 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>140.0364685058594</v>
+        <v>138.8740539550781</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -796,7 +796,7 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>157.5316925048828</v>
+        <v>156.6345367431641</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -808,7 +808,7 @@
         <v>20</v>
       </c>
       <c r="F16">
-        <v>139.5316925048828</v>
+        <v>138.6345367431641</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -816,7 +816,7 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>157.7234039306641</v>
+        <v>156.6550750732422</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -828,7 +828,7 @@
         <v>20</v>
       </c>
       <c r="F17">
-        <v>139.7234039306641</v>
+        <v>138.6550750732422</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -836,7 +836,7 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>157.3439025878906</v>
+        <v>156.6184997558594</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -848,7 +848,7 @@
         <v>20</v>
       </c>
       <c r="F18">
-        <v>139.3439025878906</v>
+        <v>138.6184997558594</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -856,7 +856,7 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>157.4517822265625</v>
+        <v>156.6291809082031</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -868,7 +868,7 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>139.4517822265625</v>
+        <v>138.6291809082031</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -876,7 +876,7 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>157.6978454589844</v>
+        <v>156.7843627929688</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -888,7 +888,7 @@
         <v>20</v>
       </c>
       <c r="F20">
-        <v>139.6978454589844</v>
+        <v>138.7843627929688</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -896,7 +896,7 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>157.5846862792969</v>
+        <v>156.6518249511719</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -908,7 +908,7 @@
         <v>20</v>
       </c>
       <c r="F21">
-        <v>139.5846862792969</v>
+        <v>138.6518249511719</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -916,7 +916,7 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>157.5492248535156</v>
+        <v>156.6193389892578</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -928,7 +928,7 @@
         <v>20</v>
       </c>
       <c r="F22">
-        <v>139.5492248535156</v>
+        <v>138.6193389892578</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -936,7 +936,7 @@
         <v>27</v>
       </c>
       <c r="B23">
-        <v>157.6785430908203</v>
+        <v>156.703125</v>
       </c>
       <c r="C23">
         <v>20</v>
@@ -948,7 +948,7 @@
         <v>20</v>
       </c>
       <c r="F23">
-        <v>139.6785430908203</v>
+        <v>138.703125</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -956,7 +956,7 @@
         <v>28</v>
       </c>
       <c r="B24">
-        <v>157.8500823974609</v>
+        <v>156.7980346679688</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -968,7 +968,7 @@
         <v>20</v>
       </c>
       <c r="F24">
-        <v>139.8500823974609</v>
+        <v>138.7980346679688</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -976,7 +976,7 @@
         <v>29</v>
       </c>
       <c r="B25">
-        <v>295.937744140625</v>
+        <v>309.4971618652344</v>
       </c>
       <c r="C25">
         <v>250</v>
@@ -988,7 +988,7 @@
         <v>300</v>
       </c>
       <c r="F25">
-        <v>170.937744140625</v>
+        <v>184.4971618652344</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -996,7 +996,7 @@
         <v>30</v>
       </c>
       <c r="B26">
-        <v>328.7368774414062</v>
+        <v>356.6873474121094</v>
       </c>
       <c r="C26">
         <v>250</v>
@@ -1008,7 +1008,7 @@
         <v>300</v>
       </c>
       <c r="F26">
-        <v>203.7368774414062</v>
+        <v>231.6873474121094</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1016,7 +1016,7 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>329.1467590332031</v>
+        <v>357.426513671875</v>
       </c>
       <c r="C27">
         <v>250</v>
@@ -1028,7 +1028,7 @@
         <v>300</v>
       </c>
       <c r="F27">
-        <v>204.1467590332031</v>
+        <v>232.426513671875</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1036,7 +1036,7 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <v>356.8616638183594</v>
+        <v>397.2751159667969</v>
       </c>
       <c r="C28">
         <v>250</v>
@@ -1048,7 +1048,7 @@
         <v>300</v>
       </c>
       <c r="F28">
-        <v>231.8616638183594</v>
+        <v>272.2751159667969</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1056,7 +1056,7 @@
         <v>33</v>
       </c>
       <c r="B29">
-        <v>295.7943115234375</v>
+        <v>309.1565856933594</v>
       </c>
       <c r="C29">
         <v>250</v>
@@ -1068,7 +1068,7 @@
         <v>300</v>
       </c>
       <c r="F29">
-        <v>170.7943115234375</v>
+        <v>184.1565856933594</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1076,7 +1076,7 @@
         <v>34</v>
       </c>
       <c r="B30">
-        <v>328.1439514160156</v>
+        <v>354.9096984863281</v>
       </c>
       <c r="C30">
         <v>250</v>
@@ -1088,7 +1088,7 @@
         <v>300</v>
       </c>
       <c r="F30">
-        <v>203.1439514160156</v>
+        <v>229.9096984863281</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1096,7 +1096,7 @@
         <v>35</v>
       </c>
       <c r="B31">
-        <v>328.3083190917969</v>
+        <v>355.4646911621094</v>
       </c>
       <c r="C31">
         <v>250</v>
@@ -1108,7 +1108,7 @@
         <v>300</v>
       </c>
       <c r="F31">
-        <v>203.3083190917969</v>
+        <v>230.4646911621094</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1116,7 +1116,7 @@
         <v>36</v>
       </c>
       <c r="B32">
-        <v>329.407470703125</v>
+        <v>356.3917846679688</v>
       </c>
       <c r="C32">
         <v>250</v>
@@ -1128,7 +1128,7 @@
         <v>300</v>
       </c>
       <c r="F32">
-        <v>204.407470703125</v>
+        <v>231.3917846679688</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1136,7 +1136,7 @@
         <v>37</v>
       </c>
       <c r="B33">
-        <v>297.2477111816406</v>
+        <v>310.7924194335938</v>
       </c>
       <c r="C33">
         <v>250</v>
@@ -1148,7 +1148,7 @@
         <v>300</v>
       </c>
       <c r="F33">
-        <v>172.2477111816406</v>
+        <v>185.7924194335938</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1156,7 +1156,7 @@
         <v>38</v>
       </c>
       <c r="B34">
-        <v>296.6250915527344</v>
+        <v>310.2366638183594</v>
       </c>
       <c r="C34">
         <v>250</v>
@@ -1168,7 +1168,7 @@
         <v>300</v>
       </c>
       <c r="F34">
-        <v>171.6250915527344</v>
+        <v>185.2366638183594</v>
       </c>
     </row>
   </sheetData>

--- a/MRP_AI_Predictions.xlsx
+++ b/MRP_AI_Predictions.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Manoj\Engineering\Btech\4th year\tata-tech\tata-supply-chain\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721D0C44-8B6E-41B3-9927-E429884F6DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Material</t>
   </si>
@@ -131,13 +137,16 @@
   </si>
   <si>
     <t>RM-200020</t>
+  </si>
+  <si>
+    <t>Lead Time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,13 +162,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="DM Sans"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -189,10 +211,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -200,13 +228,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -244,7 +280,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -278,6 +314,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -312,9 +349,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -487,11 +525,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,13 +556,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>152.2281341552734</v>
+        <v>152.22813415527341</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -528,10 +577,13 @@
         <v>60</v>
       </c>
       <c r="F2">
-        <v>75.22813415527344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>75.228134155273438</v>
+      </c>
+      <c r="G2" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -548,15 +600,18 @@
         <v>80</v>
       </c>
       <c r="F3">
-        <v>79.72311401367188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>79.723114013671875</v>
+      </c>
+      <c r="G3" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
-        <v>315.9134216308594</v>
+        <v>315.91342163085938</v>
       </c>
       <c r="C4">
         <v>250</v>
@@ -570,8 +625,11 @@
       <c r="F4">
         <v>-9.086578369140625</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -590,8 +648,11 @@
       <c r="F5">
         <v>134.5955505371094</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -610,8 +671,11 @@
       <c r="F6">
         <v>134.7098388671875</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -630,13 +694,16 @@
       <c r="F7">
         <v>134.8041076660156</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
-        <v>151.3575897216797</v>
+        <v>151.35758972167969</v>
       </c>
       <c r="C8">
         <v>25</v>
@@ -648,10 +715,13 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>134.3575897216797</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>134.35758972167969</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -670,13 +740,16 @@
       <c r="F9">
         <v>134.80029296875</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>151.5839385986328</v>
+        <v>151.58393859863281</v>
       </c>
       <c r="C10">
         <v>25</v>
@@ -688,15 +761,18 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>134.5839385986328</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>134.58393859863281</v>
+      </c>
+      <c r="G10" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11">
-        <v>151.9650268554688</v>
+        <v>151.96502685546881</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -708,10 +784,13 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>134.9650268554688</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>134.96502685546881</v>
+      </c>
+      <c r="G11" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -730,13 +809,16 @@
       <c r="F12">
         <v>134.5505676269531</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13">
-        <v>151.8899536132812</v>
+        <v>151.88995361328119</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -748,15 +830,18 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>134.8899536132812</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>134.88995361328119</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14">
-        <v>151.6146850585938</v>
+        <v>151.61468505859381</v>
       </c>
       <c r="C14">
         <v>25</v>
@@ -768,10 +853,13 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>134.6146850585938</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>134.61468505859381</v>
+      </c>
+      <c r="G14" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -790,13 +878,16 @@
       <c r="F15">
         <v>138.8740539550781</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16">
-        <v>156.6345367431641</v>
+        <v>156.63453674316409</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -808,15 +899,18 @@
         <v>20</v>
       </c>
       <c r="F16">
-        <v>138.6345367431641</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>138.63453674316409</v>
+      </c>
+      <c r="G16" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17">
-        <v>156.6550750732422</v>
+        <v>156.65507507324219</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -828,10 +922,13 @@
         <v>20</v>
       </c>
       <c r="F17">
-        <v>138.6550750732422</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>138.65507507324219</v>
+      </c>
+      <c r="G17" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -850,8 +947,11 @@
       <c r="F18">
         <v>138.6184997558594</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -870,13 +970,16 @@
       <c r="F19">
         <v>138.6291809082031</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20">
-        <v>156.7843627929688</v>
+        <v>156.78436279296881</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -888,10 +991,13 @@
         <v>20</v>
       </c>
       <c r="F20">
-        <v>138.7843627929688</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>138.78436279296881</v>
+      </c>
+      <c r="G20" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -910,13 +1016,16 @@
       <c r="F21">
         <v>138.6518249511719</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
       <c r="B22">
-        <v>156.6193389892578</v>
+        <v>156.61933898925781</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -928,10 +1037,13 @@
         <v>20</v>
       </c>
       <c r="F22">
-        <v>138.6193389892578</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>138.61933898925781</v>
+      </c>
+      <c r="G22" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -950,13 +1062,16 @@
       <c r="F23">
         <v>138.703125</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24">
-        <v>156.7980346679688</v>
+        <v>156.79803466796881</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -968,15 +1083,18 @@
         <v>20</v>
       </c>
       <c r="F24">
-        <v>138.7980346679688</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>138.79803466796881</v>
+      </c>
+      <c r="G24" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
       <c r="B25">
-        <v>309.4971618652344</v>
+        <v>309.49716186523438</v>
       </c>
       <c r="C25">
         <v>250</v>
@@ -990,13 +1108,16 @@
       <c r="F25">
         <v>184.4971618652344</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
       <c r="B26">
-        <v>356.6873474121094</v>
+        <v>356.68734741210938</v>
       </c>
       <c r="C26">
         <v>250</v>
@@ -1010,8 +1131,11 @@
       <c r="F26">
         <v>231.6873474121094</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1030,13 +1154,16 @@
       <c r="F27">
         <v>232.426513671875</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
       <c r="B28">
-        <v>397.2751159667969</v>
+        <v>397.27511596679688</v>
       </c>
       <c r="C28">
         <v>250</v>
@@ -1048,15 +1175,18 @@
         <v>300</v>
       </c>
       <c r="F28">
-        <v>272.2751159667969</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>272.27511596679688</v>
+      </c>
+      <c r="G28" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
       <c r="B29">
-        <v>309.1565856933594</v>
+        <v>309.15658569335938</v>
       </c>
       <c r="C29">
         <v>250</v>
@@ -1070,13 +1200,16 @@
       <c r="F29">
         <v>184.1565856933594</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30">
-        <v>354.9096984863281</v>
+        <v>354.90969848632813</v>
       </c>
       <c r="C30">
         <v>250</v>
@@ -1090,13 +1223,16 @@
       <c r="F30">
         <v>229.9096984863281</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
       <c r="B31">
-        <v>355.4646911621094</v>
+        <v>355.46469116210938</v>
       </c>
       <c r="C31">
         <v>250</v>
@@ -1110,13 +1246,16 @@
       <c r="F31">
         <v>230.4646911621094</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
       <c r="B32">
-        <v>356.3917846679688</v>
+        <v>356.39178466796881</v>
       </c>
       <c r="C32">
         <v>250</v>
@@ -1128,15 +1267,18 @@
         <v>300</v>
       </c>
       <c r="F32">
-        <v>231.3917846679688</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>231.39178466796881</v>
+      </c>
+      <c r="G32" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
       <c r="B33">
-        <v>310.7924194335938</v>
+        <v>310.79241943359381</v>
       </c>
       <c r="C33">
         <v>250</v>
@@ -1148,15 +1290,18 @@
         <v>300</v>
       </c>
       <c r="F33">
-        <v>185.7924194335938</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>185.79241943359381</v>
+      </c>
+      <c r="G33" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
       <c r="B34">
-        <v>310.2366638183594</v>
+        <v>310.23666381835938</v>
       </c>
       <c r="C34">
         <v>250</v>
@@ -1169,6 +1314,9 @@
       </c>
       <c r="F34">
         <v>185.2366638183594</v>
+      </c>
+      <c r="G34" s="3">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
